--- a/artfynd/A 45811-2022 artfynd.xlsx
+++ b/artfynd/A 45811-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45811-2022 artfynd.xlsx
+++ b/artfynd/A 45811-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3789412</v>
+        <v>88153</v>
       </c>
       <c r="B2" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kärven SV-ut, mellan Gubbnoret och Andaskärret, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>695686.5309165103</v>
+        <v>695687</v>
       </c>
       <c r="R2" t="n">
-        <v>6653518.887392881</v>
+        <v>6653519</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,24 +757,14 @@
           <t>2011-09-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-09-04</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Växer invid stig, i gallrad yngre blandskog på frisk mark.</t>
+          <t>Nyfynd. Växer invid stig, i gallrad yngre blandskog på frisk mark.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2486342</v>
+        <v>2929724</v>
       </c>
       <c r="B3" t="n">
-        <v>104654</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220015</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Campanula latifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>695686.5309165103</v>
+        <v>695498</v>
       </c>
       <c r="R3" t="n">
-        <v>6653518.887392881</v>
+        <v>6653377</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,24 +864,14 @@
           <t>2011-09-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-09-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer invid stig, i gallrad yngre blandskog på frisk mark.</t>
+          <t>Invid stig i planterad ungskog av gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +885,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blandskog, gallrad</t>
+          <t>Granskog, ungskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4240774</v>
+        <v>2486342</v>
       </c>
       <c r="B4" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107719</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,16 +914,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222002</v>
+        <v>220015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Hässleklocka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Campanula latifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>695497.6373750935</v>
+        <v>695687</v>
       </c>
       <c r="R4" t="n">
-        <v>6653366.923964093</v>
+        <v>6653519</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,24 +971,14 @@
           <t>2011-09-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-09-04</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Invid stig i planterad ungskog av gran.</t>
+          <t>Växer invid stig, i gallrad yngre blandskog på frisk mark.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +992,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Granskog, ungskog</t>
+          <t>Blandskog, gallrad</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,67 +1010,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88153</v>
+        <v>3507319</v>
       </c>
       <c r="B5" t="n">
-        <v>97512</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>174</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kärven SV-ut, mellan Gubbnoret och Andaskärret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695686.5309165103</v>
+        <v>695687</v>
       </c>
       <c r="R5" t="n">
-        <v>6653518.887392881</v>
+        <v>6653519</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,24 +1078,14 @@
           <t>2011-09-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-09-04</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Nyfynd. Växer invid stig, i gallrad yngre blandskog på frisk mark.</t>
+          <t>Växer invid stig, i gallrad yngre blandskog på frisk mark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,15 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4818725</v>
+        <v>3789412</v>
       </c>
       <c r="B6" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,21 +1128,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>221423</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1217,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695686.5309165103</v>
+        <v>695687</v>
       </c>
       <c r="R6" t="n">
-        <v>6653518.887392881</v>
+        <v>6653519</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1250,19 +1185,9 @@
           <t>2011-09-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2011-09-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1299,32 +1224,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3507319</v>
+        <v>4240774</v>
       </c>
       <c r="B7" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>222002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1339,13 +1259,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>695686.5309165103</v>
+        <v>695498</v>
       </c>
       <c r="R7" t="n">
-        <v>6653518.887392881</v>
+        <v>6653367</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,24 +1292,14 @@
           <t>2011-09-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2011-09-04</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växer invid stig, i gallrad yngre blandskog på frisk mark.</t>
+          <t>Invid stig i planterad ungskog av gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,7 +1313,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Blandskog, gallrad</t>
+          <t>Granskog, ungskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1421,37 +1331,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5767984</v>
+        <v>4818725</v>
       </c>
       <c r="B8" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223246</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1461,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695686.5309165103</v>
+        <v>695687</v>
       </c>
       <c r="R8" t="n">
-        <v>6653518.887392881</v>
+        <v>6653519</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1494,19 +1399,9 @@
           <t>2011-09-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2011-09-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1540,6 +1435,113 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5767984</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kärven SV-ut, mellan Gubbnoret och Andaskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>695687</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6653519</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2011-09-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2011-09-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer invid stig, i gallrad yngre blandskog på frisk mark.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Blandskog, gallrad</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45811-2022 artfynd.xlsx
+++ b/artfynd/A 45811-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88153</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2929724</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2486342</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3507319</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3789412</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4240774</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4818725</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,8 +1582,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5767984</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>